--- a/Unity/Assets/Config/Excel/Datas/UnitConfig.xlsx
+++ b/Unity/Assets/Config/Excel/Datas/UnitConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22650" windowHeight="12015"/>
+    <workbookView windowWidth="22080" windowHeight="12180"/>
   </bookViews>
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="37">
   <si>
     <t>##var</t>
   </si>
@@ -59,6 +59,9 @@
     <t>int</t>
   </si>
   <si>
+    <t>EUnitType</t>
+  </si>
+  <si>
     <t>text</t>
   </si>
   <si>
@@ -74,6 +77,9 @@
     <t>##</t>
   </si>
   <si>
+    <t>类型</t>
+  </si>
+  <si>
     <t>测试说明</t>
   </si>
   <si>
@@ -90,6 +96,9 @@
   </si>
   <si>
     <t>体重</t>
+  </si>
+  <si>
+    <t>Player</t>
   </si>
   <si>
     <t>UnitConfig.Name.1001</t>
@@ -1177,73 +1186,73 @@
         <v>9</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" s="6"/>
       <c r="G2" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="13.5" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="2:10">
       <c r="B4" s="3">
         <v>1001</v>
       </c>
-      <c r="C4" s="3">
-        <v>1</v>
+      <c r="C4" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H4" s="3">
         <v>1</v>
@@ -1259,20 +1268,20 @@
       <c r="B5" s="3">
         <v>1002</v>
       </c>
-      <c r="C5" s="3">
-        <v>1</v>
+      <c r="C5" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H5" s="8">
         <v>2</v>
@@ -1288,20 +1297,20 @@
       <c r="B6" s="3">
         <v>1003</v>
       </c>
-      <c r="C6" s="3">
-        <v>1</v>
+      <c r="C6" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H6" s="3">
         <v>1</v>
@@ -1318,20 +1327,20 @@
       <c r="B7" s="3">
         <v>1004</v>
       </c>
-      <c r="C7" s="3">
-        <v>1</v>
+      <c r="C7" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H7" s="8">
         <v>2</v>

--- a/Unity/Assets/Config/Excel/Datas/UnitConfig.xlsx
+++ b/Unity/Assets/Config/Excel/Datas/UnitConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="39">
   <si>
     <t>##var</t>
   </si>
@@ -138,6 +138,12 @@
   </si>
   <si>
     <t>带有强力攻击技能4</t>
+  </si>
+  <si>
+    <t>Bullet</t>
+  </si>
+  <si>
+    <t>UnitConfig.Name.5001</t>
   </si>
 </sst>
 </file>
@@ -1134,8 +1140,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
+  <dimension ref="A1:J8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="21.1666666666667" style="4" customWidth="1"/>
     <col min="2" max="3" width="12.6666666666667" style="4" customWidth="1"/>
@@ -1283,7 +1289,7 @@
       <c r="G5" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="H5" s="8">
+      <c r="H5" s="3">
         <v>2</v>
       </c>
       <c r="I5" s="8">
@@ -1313,10 +1319,10 @@
         <v>33</v>
       </c>
       <c r="H6" s="3">
-        <v>1</v>
-      </c>
-      <c r="I6" s="3">
-        <v>178</v>
+        <v>3</v>
+      </c>
+      <c r="I6" s="8">
+        <v>279</v>
       </c>
       <c r="J6" s="3">
         <v>68</v>
@@ -1342,13 +1348,43 @@
       <c r="G7" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="8">
-        <v>2</v>
+      <c r="H7" s="3">
+        <v>4</v>
       </c>
       <c r="I7" s="8">
         <v>278</v>
       </c>
       <c r="J7" s="8">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="8"/>
+      <c r="B8" s="3">
+        <v>5001</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8" s="3">
+        <v>4</v>
+      </c>
+      <c r="I8" s="8">
+        <v>278</v>
+      </c>
+      <c r="J8" s="8">
         <v>78</v>
       </c>
     </row>

--- a/Unity/Assets/Config/Excel/Datas/UnitConfig.xlsx
+++ b/Unity/Assets/Config/Excel/Datas/UnitConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="41">
   <si>
     <t>##var</t>
   </si>
@@ -138,6 +138,12 @@
   </si>
   <si>
     <t>带有强力攻击技能4</t>
+  </si>
+  <si>
+    <t>Food</t>
+  </si>
+  <si>
+    <t>UnitConfig.Name.2001</t>
   </si>
   <si>
     <t>Bullet</t>
@@ -1140,8 +1146,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="7"/>
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.1666666666667" style="4" customWidth="1"/>
     <col min="2" max="3" width="12.6666666666667" style="4" customWidth="1"/>
@@ -1358,33 +1364,62 @@
         <v>78</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="8"/>
+    <row r="8" spans="2:10">
       <c r="B8" s="3">
-        <v>5001</v>
+        <v>2001</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H8" s="3">
+        <v>1</v>
+      </c>
+      <c r="I8" s="3">
+        <v>178</v>
+      </c>
+      <c r="J8" s="3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="8"/>
+      <c r="B9" s="3">
+        <v>5001</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="F8" s="8" t="s">
+      <c r="E9" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G9" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H9" s="3">
         <v>4</v>
       </c>
-      <c r="I8" s="8">
+      <c r="I9" s="8">
         <v>278</v>
       </c>
-      <c r="J8" s="8">
+      <c r="J9" s="8">
         <v>78</v>
       </c>
     </row>

--- a/Unity/Assets/Config/Excel/Datas/UnitConfig.xlsx
+++ b/Unity/Assets/Config/Excel/Datas/UnitConfig.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t>##var</t>
   </si>
@@ -53,6 +53,15 @@
     <t>Weight</t>
   </si>
   <si>
+    <t>Hp</t>
+  </si>
+  <si>
+    <t>Attack</t>
+  </si>
+  <si>
+    <t>Speed</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -74,6 +83,9 @@
     <t>int&amp;group=s</t>
   </si>
   <si>
+    <t>float&amp;group=s</t>
+  </si>
+  <si>
     <t>##</t>
   </si>
   <si>
@@ -98,6 +110,15 @@
     <t>体重</t>
   </si>
   <si>
+    <t>生命值</t>
+  </si>
+  <si>
+    <t>攻击力</t>
+  </si>
+  <si>
+    <t>速度</t>
+  </si>
+  <si>
     <t>Player</t>
   </si>
   <si>
@@ -150,6 +171,21 @@
   </si>
   <si>
     <t>UnitConfig.Name.5001</t>
+  </si>
+  <si>
+    <t>Monster</t>
+  </si>
+  <si>
+    <t>战斗AI测试怪</t>
+  </si>
+  <si>
+    <t>UnitConfig.Name.3001</t>
+  </si>
+  <si>
+    <t>训练假人</t>
+  </si>
+  <si>
+    <t>默认用于验证ARPG战斗AI</t>
   </si>
 </sst>
 </file>
@@ -630,172 +666,172 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="23" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+  <cellXfs count="49">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="1" xfId="22" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="3" applyFill="1" borderId="0" applyBorder="1" xfId="23" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="1" xfId="22" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="23" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="3" applyFill="1" borderId="0" applyBorder="1" xfId="23" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="4" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1144,26 +1180,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <sheetPr/>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="21.1666666666667" style="4" customWidth="1"/>
-    <col min="2" max="3" width="12.6666666666667" style="4" customWidth="1"/>
-    <col min="4" max="4" width="17.1666666666667" style="4" customWidth="1"/>
-    <col min="5" max="5" width="18.6666666666667" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.6666666666667" style="4" customWidth="1"/>
-    <col min="7" max="7" width="21.3333333333333" style="4" customWidth="1"/>
-    <col min="8" max="8" width="9.66666666666667" style="4" customWidth="1"/>
-    <col min="9" max="9" width="28.6666666666667" style="4" customWidth="1"/>
-    <col min="10" max="10" width="7.83333333333333" style="4" customWidth="1"/>
-    <col min="11" max="11" width="6.5" style="4" customWidth="1"/>
-    <col min="12" max="12" width="6.66666666666667" style="4" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="4"/>
+    <col min="1" max="1" width="21.1666666666667" customWidth="1" style="4"/>
+    <col min="2" max="3" width="12.6666666666667" customWidth="1" style="4"/>
+    <col min="4" max="4" width="17.1666666666667" customWidth="1" style="4"/>
+    <col min="5" max="5" width="18.6666666666667" customWidth="1" style="4"/>
+    <col min="6" max="6" width="12.6666666666667" customWidth="1" style="4"/>
+    <col min="7" max="7" width="21.3333333333333" customWidth="1" style="4"/>
+    <col min="8" max="8" width="9.66666666666667" customWidth="1" style="4"/>
+    <col min="9" max="9" width="28.6666666666667" customWidth="1" style="4"/>
+    <col min="10" max="10" width="7.83333333333333" customWidth="1" style="4"/>
+    <col min="11" max="11" width="6.5" customWidth="1" style="4"/>
+    <col min="12" max="12" width="6.66666666666667" customWidth="1" style="4"/>
+    <col min="13" max="16384" width="9" customWidth="1" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="13.5" spans="1:10">
+    <row r="1" ht="13.5" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1189,82 +1225,109 @@
       <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="K1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" s="2" customFormat="1" ht="13.5" spans="1:10">
+    <row r="2" ht="13.5" s="2" customFormat="1">
       <c r="A2" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F2" s="6"/>
       <c r="G2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>9</v>
-      </c>
       <c r="I2" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="13.5" spans="1:10">
+    <row r="3" ht="13.5" s="1" customFormat="1">
       <c r="A3" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="4" spans="2:10">
+    <row r="4">
       <c r="B4" s="3">
         <v>1001</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="H4" s="3">
         <v>1</v>
@@ -1275,25 +1338,34 @@
       <c r="J4" s="3">
         <v>68</v>
       </c>
+      <c r="K4" s="4">
+        <v>68</v>
+      </c>
+      <c r="L4" s="4">
+        <v>10</v>
+      </c>
+      <c r="M4" s="4">
+        <v>5</v>
+      </c>
     </row>
-    <row r="5" spans="2:10">
+    <row r="5">
       <c r="B5" s="3">
         <v>1002</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="H5" s="3">
         <v>2</v>
@@ -1304,25 +1376,34 @@
       <c r="J5" s="8">
         <v>78</v>
       </c>
+      <c r="K5" s="4">
+        <v>78</v>
+      </c>
+      <c r="L5" s="4">
+        <v>10</v>
+      </c>
+      <c r="M5" s="4">
+        <v>5</v>
+      </c>
     </row>
-    <row r="6" s="3" customFormat="1" spans="2:10">
+    <row r="6" s="3" customFormat="1">
       <c r="B6" s="3">
         <v>1003</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H6" s="3">
         <v>3</v>
@@ -1333,26 +1414,35 @@
       <c r="J6" s="3">
         <v>68</v>
       </c>
+      <c r="K6" s="3">
+        <v>68</v>
+      </c>
+      <c r="L6" s="3">
+        <v>10</v>
+      </c>
+      <c r="M6" s="3">
+        <v>5</v>
+      </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7">
       <c r="A7" s="8"/>
       <c r="B7" s="3">
         <v>1004</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="H7" s="3">
         <v>4</v>
@@ -1363,25 +1453,34 @@
       <c r="J7" s="8">
         <v>78</v>
       </c>
+      <c r="K7" s="4">
+        <v>78</v>
+      </c>
+      <c r="L7" s="4">
+        <v>10</v>
+      </c>
+      <c r="M7" s="4">
+        <v>5</v>
+      </c>
     </row>
-    <row r="8" spans="2:10">
+    <row r="8">
       <c r="B8" s="3">
         <v>2001</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="H8" s="3">
         <v>1</v>
@@ -1392,26 +1491,35 @@
       <c r="J8" s="3">
         <v>68</v>
       </c>
+      <c r="K8" s="4">
+        <v>1</v>
+      </c>
+      <c r="L8" s="4">
+        <v>0</v>
+      </c>
+      <c r="M8" s="4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9">
       <c r="A9" s="8"/>
       <c r="B9" s="3">
         <v>5001</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="H9" s="3">
         <v>4</v>
@@ -1422,9 +1530,56 @@
       <c r="J9" s="8">
         <v>78</v>
       </c>
+      <c r="K9" s="4">
+        <v>1</v>
+      </c>
+      <c r="L9" s="4">
+        <v>0</v>
+      </c>
+      <c r="M9" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="4">
+        <v>3001</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H10" s="4">
+        <v>5</v>
+      </c>
+      <c r="I10" s="4">
+        <v>180</v>
+      </c>
+      <c r="J10" s="4">
+        <v>72</v>
+      </c>
+      <c r="K10" s="4">
+        <v>120</v>
+      </c>
+      <c r="L10" s="4">
+        <v>8</v>
+      </c>
+      <c r="M10" s="4">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="E3:F3"/>

--- a/Unity/Assets/Config/Excel/Datas/UnitConfig.xlsx
+++ b/Unity/Assets/Config/Excel/Datas/UnitConfig.xlsx
@@ -1,371 +1,192 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22080" windowHeight="12180"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="22080" windowHeight="12180" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
+    <sheet name="UnitProto" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
-  <si>
-    <t>##var</t>
-  </si>
-  <si>
-    <t>Id</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>##Desc</t>
-  </si>
-  <si>
-    <t>Position</t>
-  </si>
-  <si>
-    <t>Height</t>
-  </si>
-  <si>
-    <t>Weight</t>
-  </si>
-  <si>
-    <t>Hp</t>
-  </si>
-  <si>
-    <t>Attack</t>
-  </si>
-  <si>
-    <t>Speed</t>
-  </si>
-  <si>
-    <t>##type</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>EUnitType</t>
-  </si>
-  <si>
-    <t>text</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>int&amp;group=c</t>
-  </si>
-  <si>
-    <t>int&amp;group=s</t>
-  </si>
-  <si>
-    <t>float&amp;group=s</t>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>类型</t>
-  </si>
-  <si>
-    <t>测试说明</t>
-  </si>
-  <si>
-    <t>名字</t>
-  </si>
-  <si>
-    <t>描述</t>
-  </si>
-  <si>
-    <t>位置</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>体重</t>
-  </si>
-  <si>
-    <t>生命值</t>
-  </si>
-  <si>
-    <t>攻击力</t>
-  </si>
-  <si>
-    <t>速度</t>
-  </si>
-  <si>
-    <t>Player</t>
-  </si>
-  <si>
-    <t>UnitConfig.Name.1001</t>
-  </si>
-  <si>
-    <t>米克尔</t>
-  </si>
-  <si>
-    <t>带有强力攻击技能</t>
-  </si>
-  <si>
-    <t>测试说明2</t>
-  </si>
-  <si>
-    <t>UnitConfig.Name.1002</t>
-  </si>
-  <si>
-    <t>米克尔2</t>
-  </si>
-  <si>
-    <t>带有强力攻击技能2</t>
-  </si>
-  <si>
-    <t>UnitConfig.Name.1003</t>
-  </si>
-  <si>
-    <t>米克尔3</t>
-  </si>
-  <si>
-    <t>带有强力攻击技能3</t>
-  </si>
-  <si>
-    <t>UnitConfig.Name.1004</t>
-  </si>
-  <si>
-    <t>米克尔4</t>
-  </si>
-  <si>
-    <t>带有强力攻击技能4</t>
-  </si>
-  <si>
-    <t>Food</t>
-  </si>
-  <si>
-    <t>UnitConfig.Name.2001</t>
-  </si>
-  <si>
-    <t>Bullet</t>
-  </si>
-  <si>
-    <t>UnitConfig.Name.5001</t>
-  </si>
-  <si>
-    <t>Monster</t>
-  </si>
-  <si>
-    <t>战斗AI测试怪</t>
-  </si>
-  <si>
-    <t>UnitConfig.Name.3001</t>
-  </si>
-  <si>
-    <t>训练假人</t>
-  </si>
-  <si>
-    <t>默认用于验证ARPG战斗AI</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color rgb="FF006100"/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color rgb="FF9C0006"/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
+      <color theme="1"/>
       <sz val="9"/>
-      <color rgb="FF000000"/>
+    </font>
+    <font>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <u/>
+      <color rgb="FF000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
+      <color rgb="FF800080"/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color rgb="FFFF0000"/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
       <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <color rgb="FF3F3F76"/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <b val="1"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color rgb="FF9C6500"/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <color theme="0"/>
       <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -666,172 +487,172 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="49">
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="1" xfId="22" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="3" applyFill="1" borderId="0" applyBorder="1" xfId="23" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+  <cellXfs count="10">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="22"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="23"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="1" xfId="22" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="22">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="3" applyFill="1" borderId="0" applyBorder="1" xfId="23" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="23">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="4" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -887,11 +708,74 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1180,412 +1064,599 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <sheetPr/>
-  <dimension ref="A1:M10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N10"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="21.1666666666667" customWidth="1" style="4"/>
-    <col min="2" max="3" width="12.6666666666667" customWidth="1" style="4"/>
-    <col min="4" max="4" width="17.1666666666667" customWidth="1" style="4"/>
-    <col min="5" max="5" width="18.6666666666667" customWidth="1" style="4"/>
-    <col min="6" max="6" width="12.6666666666667" customWidth="1" style="4"/>
-    <col min="7" max="7" width="21.3333333333333" customWidth="1" style="4"/>
-    <col min="8" max="8" width="9.66666666666667" customWidth="1" style="4"/>
-    <col min="9" max="9" width="28.6666666666667" customWidth="1" style="4"/>
-    <col min="10" max="10" width="7.83333333333333" customWidth="1" style="4"/>
-    <col min="11" max="11" width="6.5" customWidth="1" style="4"/>
-    <col min="12" max="12" width="6.66666666666667" customWidth="1" style="4"/>
-    <col min="13" max="16384" width="9" customWidth="1" style="4"/>
+    <col width="21.1666666666667" customWidth="1" style="4" min="1" max="1"/>
+    <col width="12.6666666666667" customWidth="1" style="4" min="2" max="3"/>
+    <col width="17.1666666666667" customWidth="1" style="4" min="4" max="4"/>
+    <col width="18.6666666666667" customWidth="1" style="4" min="5" max="5"/>
+    <col width="12.6666666666667" customWidth="1" style="4" min="6" max="6"/>
+    <col width="21.3333333333333" customWidth="1" style="4" min="7" max="7"/>
+    <col width="9.66666666666667" customWidth="1" style="4" min="8" max="8"/>
+    <col width="28.6666666666667" customWidth="1" style="4" min="9" max="9"/>
+    <col width="7.83333333333333" customWidth="1" style="4" min="10" max="10"/>
+    <col width="6.5" customWidth="1" style="4" min="11" max="11"/>
+    <col width="6.66666666666667" customWidth="1" style="4" min="12" max="12"/>
+    <col width="9" customWidth="1" style="4" min="13" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.5" s="1" customFormat="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="5"/>
-      <c r="G1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>10</v>
+    <row r="1" ht="13.5" customFormat="1" customHeight="1" s="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>##Desc</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Position</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Hp</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ResName</t>
+        </is>
       </c>
     </row>
-    <row r="2" ht="13.5" s="2" customFormat="1">
-      <c r="A2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="6"/>
-      <c r="G2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>18</v>
+    <row r="2" ht="13.5" customFormat="1" customHeight="1" s="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>EUnitType</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>int&amp;group=c</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>int&amp;group=s</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>int&amp;group=s</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>int&amp;group=s</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>float&amp;group=s</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
       </c>
     </row>
-    <row r="3" ht="13.5" s="1" customFormat="1">
-      <c r="A3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>29</v>
+    <row r="3" ht="13.5" customFormat="1" customHeight="1" s="1">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>测试说明</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>名字</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>描述</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
+          <t>体重</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>生命值</t>
+        </is>
+      </c>
+      <c r="L3" s="1" t="inlineStr">
+        <is>
+          <t>攻击力</t>
+        </is>
+      </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>速度</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>ResName</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="3">
+      <c r="B4" s="3" t="n">
         <v>1001</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H4" s="3">
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>测试说明</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>UnitConfig.Name.1001</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>米克尔</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>带有强力攻击技能</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I4" s="3" t="n">
         <v>178</v>
       </c>
-      <c r="J4" s="3">
+      <c r="J4" s="3" t="n">
         <v>68</v>
       </c>
-      <c r="K4" s="4">
+      <c r="K4" s="4" t="n">
         <v>68</v>
       </c>
-      <c r="L4" s="4">
+      <c r="L4" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="M4" s="4">
+      <c r="M4" s="4" t="n">
         <v>5</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Assets/Bundles/Unit/Player.prefab</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="3">
+      <c r="B5" s="3" t="n">
         <v>1002</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="H5" s="3">
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>测试说明2</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>UnitConfig.Name.1002</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>米克尔2</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>带有强力攻击技能2</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="I5" s="8">
+      <c r="I5" s="8" t="n">
         <v>278</v>
       </c>
-      <c r="J5" s="8">
+      <c r="J5" s="8" t="n">
         <v>78</v>
       </c>
-      <c r="K5" s="4">
+      <c r="K5" s="4" t="n">
         <v>78</v>
       </c>
-      <c r="L5" s="4">
+      <c r="L5" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="M5" s="4">
+      <c r="M5" s="4" t="n">
         <v>5</v>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Assets/Bundles/Unit/Player.prefab</t>
+        </is>
+      </c>
     </row>
-    <row r="6" s="3" customFormat="1">
-      <c r="B6" s="3">
+    <row r="6" customFormat="1" s="3">
+      <c r="B6" s="3" t="n">
         <v>1003</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="H6" s="3">
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>测试说明</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>UnitConfig.Name.1003</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>米克尔3</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>带有强力攻击技能3</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="I6" s="8">
+      <c r="I6" s="8" t="n">
         <v>279</v>
       </c>
-      <c r="J6" s="3">
+      <c r="J6" s="3" t="n">
         <v>68</v>
       </c>
-      <c r="K6" s="3">
+      <c r="K6" s="3" t="n">
         <v>68</v>
       </c>
-      <c r="L6" s="3">
+      <c r="L6" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="M6" s="3">
+      <c r="M6" s="3" t="n">
         <v>5</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Assets/Bundles/Unit/Player.prefab</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8"/>
-      <c r="B7" s="3">
+      <c r="A7" s="8" t="n"/>
+      <c r="B7" s="3" t="n">
         <v>1004</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H7" s="3">
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>测试说明2</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>UnitConfig.Name.1004</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>米克尔4</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>带有强力攻击技能4</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="I7" s="8">
+      <c r="I7" s="8" t="n">
         <v>278</v>
       </c>
-      <c r="J7" s="8">
+      <c r="J7" s="8" t="n">
         <v>78</v>
       </c>
-      <c r="K7" s="4">
+      <c r="K7" s="4" t="n">
         <v>78</v>
       </c>
-      <c r="L7" s="4">
+      <c r="L7" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="M7" s="4">
+      <c r="M7" s="4" t="n">
         <v>5</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Assets/Bundles/Unit/Player.prefab</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="3">
+      <c r="B8" s="3" t="n">
         <v>2001</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H8" s="3">
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>测试说明</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>UnitConfig.Name.2001</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>米克尔</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>带有强力攻击技能</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I8" s="3">
+      <c r="I8" s="3" t="n">
         <v>178</v>
       </c>
-      <c r="J8" s="3">
+      <c r="J8" s="3" t="n">
         <v>68</v>
       </c>
-      <c r="K8" s="4">
+      <c r="K8" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="L8" s="4">
+      <c r="L8" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="M8" s="4">
+      <c r="M8" s="4" t="n">
         <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Assets/Bundles/Unit/Player.prefab</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8"/>
-      <c r="B9" s="3">
+      <c r="A9" s="8" t="n"/>
+      <c r="B9" s="3" t="n">
         <v>5001</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H9" s="3">
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Bullet</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>测试说明2</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>UnitConfig.Name.5001</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>米克尔4</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>带有强力攻击技能4</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="I9" s="8">
+      <c r="I9" s="8" t="n">
         <v>278</v>
       </c>
-      <c r="J9" s="8">
+      <c r="J9" s="8" t="n">
         <v>78</v>
       </c>
-      <c r="K9" s="4">
+      <c r="K9" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="L9" s="4">
+      <c r="L9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="M9" s="4">
+      <c r="M9" s="4" t="n">
         <v>10</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Assets/Bundles/Unit/Player.prefab</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="4">
+      <c r="B10" s="4" t="n">
         <v>3001</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="H10" s="4">
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>战斗AI测试怪</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>UnitConfig.Name.3001</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>训练假人</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>默认用于验证ARPG战斗AI</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="I10" s="4">
+      <c r="I10" s="4" t="n">
         <v>180</v>
       </c>
-      <c r="J10" s="4">
+      <c r="J10" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="K10" s="4">
+      <c r="K10" s="4" t="n">
         <v>120</v>
       </c>
-      <c r="L10" s="4">
+      <c r="L10" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="M10" s="4">
+      <c r="M10" s="4" t="n">
         <v>4</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Assets/Bundles/Unit/Player.prefab</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="3">
+    <mergeCell ref="E2:F2"/>
     <mergeCell ref="E1:F1"/>
-    <mergeCell ref="E2:F2"/>
     <mergeCell ref="E3:F3"/>
   </mergeCells>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>